--- a/results/Evidencia_Experimentos.xlsx
+++ b/results/Evidencia_Experimentos.xlsx
@@ -1,22 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\Reto1-Arq.Software\results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD64B91-FF65-48FF-A8EE-3D2BE76BAAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen Exp1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Fase1 Exp1" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Fase2 Exp1" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Resumen Exp2" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Fase1 Exp2" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Fase2 Exp2" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Resumen Exp1" sheetId="1" r:id="rId1"/>
+    <sheet name="Fase1 Exp1" sheetId="2" r:id="rId2"/>
+    <sheet name="Fase2 Exp1" sheetId="3" r:id="rId3"/>
+    <sheet name="Resumen Exp2" sheetId="4" r:id="rId4"/>
+    <sheet name="Fase1 Exp2" sheetId="5" r:id="rId5"/>
+    <sheet name="Fase2 Exp2" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,157 +44,154 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="47">
   <si>
-    <t xml:space="preserve">Experimento 1 · Amortiguación Asíncrona + Canal Transaccional Prioritario</t>
+    <t>Experimento 1 · Amortiguación Asíncrona + Canal Transaccional Prioritario</t>
   </si>
   <si>
-    <t xml:space="preserve">Escenarios de calidad: Escalabilidad (órdenes/matches por minuto, latencia de cruce) y Latencia (confirmación WebSocket p95). Datos calculados a partir de los registros reales del matching-engine y del latency-probe.</t>
+    <t>Escenarios de calidad: Escalabilidad (órdenes/matches por minuto, latencia de cruce) y Latencia (confirmación WebSocket p95). Datos calculados a partir de los registros reales del matching-engine y del latency-probe.</t>
   </si>
   <si>
-    <t xml:space="preserve">Metrica</t>
+    <t>Metrica</t>
   </si>
   <si>
-    <t xml:space="preserve">Fase 1 (base)</t>
+    <t>Fase 1 (base)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fase 2 (pico)</t>
+    <t>Fase 2 (pico)</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta</t>
+    <t>Meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Veredicto</t>
+    <t>Veredicto</t>
   </si>
   <si>
-    <t xml:space="preserve">Ordenes entrantes / min</t>
+    <t>Ordenes entrantes / min</t>
   </si>
   <si>
-    <t xml:space="preserve">absorber el pico</t>
+    <t>absorber el pico</t>
   </si>
   <si>
-    <t xml:space="preserve">Emparejamientos / min</t>
+    <t>Latencia cruce interno, peor p95 por minuto (ms)</t>
   </si>
   <si>
-    <t xml:space="preserve">Latencia cruce interno, peor p95 por minuto (ms)</t>
+    <t>Latencia confirmacion WebSocket p95 (ms)</t>
   </si>
   <si>
-    <t xml:space="preserve">Latencia confirmacion WebSocket p95 (ms)</t>
+    <t>Muestras de confirmacion (n)</t>
   </si>
   <si>
-    <t xml:space="preserve">Muestras de confirmacion (n)</t>
+    <t>-</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
+    <t>Tasa de confirmaciones (conf/s)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tasa de confirmaciones (conf/s)</t>
+    <t>Peticiones fallidas (Locust)</t>
   </si>
   <si>
-    <t xml:space="preserve">Peticiones fallidas (Locust)</t>
+    <t>No disponible en estos archivos</t>
   </si>
   <si>
-    <t xml:space="preserve">No disponible en estos archivos</t>
+    <t>0%</t>
   </si>
   <si>
-    <t xml:space="preserve">0%</t>
+    <t>N/D</t>
   </si>
   <si>
-    <t xml:space="preserve">N/D</t>
+    <t>Nota: 'Peticiones fallidas', profundidad de buffer y tiempo de drenado no estaban en los archivos entregados para este experimento, así que no se reportan como CUMPLE/NO CUMPLE.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nota: 'Peticiones fallidas', profundidad de buffer y tiempo de drenado no estaban en los archivos entregados para este experimento, así que no se reportan como CUMPLE/NO CUMPLE.</t>
+    <t>Datos de la grafica comparativa</t>
   </si>
   <si>
-    <t xml:space="preserve">Datos de la grafica comparativa</t>
+    <t>Fase</t>
   </si>
   <si>
-    <t xml:space="preserve">Fase</t>
+    <t>Ordenes/min</t>
   </si>
   <si>
-    <t xml:space="preserve">Ordenes/min</t>
+    <t>Emparej./min</t>
   </si>
   <si>
-    <t xml:space="preserve">Emparej./min</t>
+    <t>Fase 1 - Linea base</t>
   </si>
   <si>
-    <t xml:space="preserve">Fase 1 - Linea base</t>
+    <t>Fase 2 - Pico</t>
   </si>
   <si>
-    <t xml:space="preserve">Fase 2 - Pico</t>
+    <t>Experimento 1 - FASE 1 (Linea Base)</t>
   </si>
   <si>
-    <t xml:space="preserve">Experimento 1 - FASE 1 (Linea Base)</t>
+    <t>Serie temporal minuto a minuto tomada del log real del matching-engine y del latency-probe.</t>
   </si>
   <si>
-    <t xml:space="preserve">Serie temporal minuto a minuto tomada del log real del matching-engine y del latency-probe.</t>
+    <t>minuto</t>
   </si>
   <si>
-    <t xml:space="preserve">minuto</t>
+    <t>orders_min</t>
   </si>
   <si>
-    <t xml:space="preserve">orders_min</t>
+    <t>matches_min</t>
   </si>
   <si>
-    <t xml:space="preserve">matches_min</t>
+    <t>core_p95_ms</t>
   </si>
   <si>
-    <t xml:space="preserve">core_p95_ms</t>
+    <t>clasificacion</t>
   </si>
   <si>
-    <t xml:space="preserve">clasificacion</t>
+    <t>rampa_fase1</t>
   </si>
   <si>
-    <t xml:space="preserve">rampa_fase1</t>
+    <t>fase1_estable</t>
   </si>
   <si>
-    <t xml:space="preserve">fase1_estable</t>
+    <t>Latencia de confirmacion (WebSocket) - minuto propio del latency-probe, no sincronizado al reloj del motor de arriba</t>
   </si>
   <si>
-    <t xml:space="preserve">Latencia de confirmacion (WebSocket) - minuto propio del latency-probe, no sincronizado al reloj del motor de arriba</t>
+    <t>minuto_probe</t>
   </si>
   <si>
-    <t xml:space="preserve">minuto_probe</t>
+    <t>n_muestras</t>
   </si>
   <si>
-    <t xml:space="preserve">n_muestras</t>
+    <t>p95_ms</t>
   </si>
   <si>
-    <t xml:space="preserve">p95_ms</t>
+    <t>Experimento 1 - FASE 2 (Pico de Volatilidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Experimento 1 - FASE 2 (Pico de Volatilidad)</t>
+    <t>meta_matches</t>
   </si>
   <si>
-    <t xml:space="preserve">meta_matches</t>
+    <t>fase2_estable</t>
   </si>
   <si>
-    <t xml:space="preserve">fase2_estable</t>
+    <t>transicion</t>
   </si>
   <si>
-    <t xml:space="preserve">transicion</t>
+    <t>Experimento 2 · Amortiguación Asíncrona + Canal Transaccional Prioritario</t>
   </si>
   <si>
-    <t xml:space="preserve">Experimento 2 · Amortiguación Asíncrona + Canal Transaccional Prioritario</t>
+    <t>Experimento 2 - FASE 1 (Linea Base)</t>
   </si>
   <si>
-    <t xml:space="preserve">Experimento 2 - FASE 1 (Linea Base)</t>
+    <t>Experimento 2 - FASE 2 (Pico de Volatilidad)</t>
   </si>
   <si>
-    <t xml:space="preserve">Experimento 2 - FASE 2 (Pico de Volatilidad)</t>
+    <t>fase2_final_parcial</t>
   </si>
   <si>
-    <t xml:space="preserve">fase2_final_parcial</t>
+    <t>amo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,86 +200,51 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="15"/>
       <color rgb="FF06764F"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF586970"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF122120"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF122120"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF8A8A8A"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF586970"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -287,7 +268,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -295,94 +276,51 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFB00020"/>
         <name val="Arial"/>
         <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
         <color rgb="FF06764F"/>
-        <sz val="10"/>
+        <name val="Arial"/>
+        <charset val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -392,12 +330,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFB00020"/>
         <name val="Arial"/>
         <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFB00020"/>
-        <sz val="10"/>
       </font>
       <fill>
         <patternFill>
@@ -405,7 +342,22 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF06764F"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE1F3EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -464,15 +416,33 @@
       <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1A272C"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -481,7 +451,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -489,7 +459,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -510,6 +480,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -519,7 +490,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Resumen Exp1'!C16</c:f>
+              <c:f>'Resumen Exp1'!$C$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -530,7 +501,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -538,15 +509,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -554,8 +533,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -564,7 +544,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Resumen Exp1'!$B$17:$B$18</c:f>
+              <c:f>'Resumen Exp1'!$B$16:$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -578,7 +558,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Resumen Exp1'!$C$17:$C$18</c:f>
+              <c:f>'Resumen Exp1'!$C$16:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -591,13 +571,18 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C25E-40CA-8224-473CAB4810E8}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Resumen Exp1'!D16</c:f>
+              <c:f>'Resumen Exp1'!$D$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -608,7 +593,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c0504d"/>
+              <a:srgbClr val="C0504D"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -616,15 +601,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -632,8 +625,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -642,7 +636,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Resumen Exp1'!$B$17:$B$18</c:f>
+              <c:f>'Resumen Exp1'!$B$16:$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -656,7 +650,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Resumen Exp1'!$D$17:$D$18</c:f>
+              <c:f>'Resumen Exp1'!$D$16:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -669,9 +663,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C25E-40CA-8224-473CAB4810E8}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="12284798"/>
         <c:axId val="39219833"/>
       </c:barChart>
@@ -699,13 +705,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="39219833"/>
@@ -749,13 +756,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="12284798"/>
@@ -783,37 +791,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -822,7 +839,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -830,7 +847,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -851,6 +868,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -859,7 +877,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase2 Exp2'!D31</c:f>
+              <c:f>'Fase2 Exp2'!$D$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -869,12 +887,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -883,15 +898,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -899,8 +922,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -908,9 +932,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase2 Exp2'!$B$32:$B$51</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
@@ -972,8 +997,8 @@
                 <c:pt idx="19">
                   <c:v>46</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1045,7 +1070,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C948-4533-B2B8-7891DCA13AA2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1053,7 +1091,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="86817870"/>
         <c:axId val="67238493"/>
       </c:lineChart>
@@ -1081,13 +1119,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="67238493"/>
@@ -1131,13 +1170,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="86817870"/>
@@ -1165,37 +1205,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1204,7 +1253,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1212,7 +1261,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1233,6 +1282,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1241,7 +1291,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase1 Exp1'!C5</c:f>
+              <c:f>'Fase1 Exp1'!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1251,12 +1301,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1265,15 +1312,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1281,8 +1336,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1290,9 +1346,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase1 Exp1'!$B$6:$B$12</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
@@ -1315,8 +1372,8 @@
                 <c:pt idx="6">
                   <c:v>10</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1349,13 +1406,18 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-86ED-4F6D-B1CD-B343FB67E368}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase1 Exp1'!D5</c:f>
+              <c:f>'Fase1 Exp1'!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1365,12 +1427,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="be4b48"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="BE4B48"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1379,15 +1438,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1395,8 +1462,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1404,9 +1472,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase1 Exp1'!$B$6:$B$12</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>4</c:v>
@@ -1429,8 +1498,8 @@
                 <c:pt idx="6">
                   <c:v>10</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1463,7 +1532,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-86ED-4F6D-B1CD-B343FB67E368}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1471,7 +1553,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="44229062"/>
         <c:axId val="96849778"/>
       </c:lineChart>
@@ -1499,13 +1581,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="96849778"/>
@@ -1549,13 +1632,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="44229062"/>
@@ -1583,37 +1667,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1622,7 +1715,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1630,7 +1723,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1651,6 +1744,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1659,7 +1753,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase1 Exp1'!D15</c:f>
+              <c:f>'Fase1 Exp1'!$D$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1669,12 +1763,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1683,15 +1774,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1699,8 +1798,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1708,9 +1808,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase1 Exp1'!$B$16:$B$24</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
@@ -1739,8 +1840,8 @@
                 <c:pt idx="8">
                   <c:v>10</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1755,7 +1856,7 @@
                   <c:v>26.48</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32.48</c:v>
+                  <c:v>32.479999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>31.26</c:v>
@@ -1779,7 +1880,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F074-4E6E-8CB6-24747BBF9EEB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1787,7 +1901,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="80000561"/>
         <c:axId val="47010043"/>
       </c:lineChart>
@@ -1815,13 +1929,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="47010043"/>
@@ -1865,13 +1980,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="80000561"/>
@@ -1899,37 +2015,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1938,7 +2063,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1946,7 +2071,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1967,6 +2092,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -1975,7 +2101,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase2 Exp1'!C5</c:f>
+              <c:f>'Fase2 Exp1'!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1985,12 +2111,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1999,15 +2122,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2015,8 +2146,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2024,9 +2156,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase2 Exp1'!$B$6:$B$29</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
@@ -2100,8 +2233,8 @@
                 <c:pt idx="23">
                   <c:v>34</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2185,13 +2318,18 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-45B2-41CC-B90C-B3E6E040DEC3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase2 Exp1'!D5</c:f>
+              <c:f>'Fase2 Exp1'!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2201,12 +2339,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="be4b48"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="BE4B48"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2215,15 +2350,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2231,8 +2374,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2240,9 +2384,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase2 Exp1'!$B$6:$B$29</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
@@ -2316,8 +2461,8 @@
                 <c:pt idx="23">
                   <c:v>34</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2401,7 +2546,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-45B2-41CC-B90C-B3E6E040DEC3}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -2409,7 +2567,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="33390351"/>
         <c:axId val="32660638"/>
       </c:lineChart>
@@ -2437,13 +2595,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="32660638"/>
@@ -2487,13 +2646,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="33390351"/>
@@ -2521,37 +2681,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2560,7 +2729,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2568,7 +2737,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -2589,6 +2758,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -2597,7 +2767,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase2 Exp1'!D32</c:f>
+              <c:f>'Fase2 Exp1'!$D$32</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2607,12 +2777,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2621,15 +2788,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -2637,8 +2812,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2646,9 +2822,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase2 Exp1'!$B$33:$B$63</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>11</c:v>
@@ -2743,8 +2920,8 @@
                 <c:pt idx="30">
                   <c:v>41</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2759,7 +2936,7 @@
                   <c:v>15.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.81</c:v>
+                  <c:v>16.809999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>15.86</c:v>
@@ -2849,7 +3026,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BF0D-4823-A75B-42BB2F1F180D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -2857,7 +3047,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="64581281"/>
         <c:axId val="89294733"/>
       </c:lineChart>
@@ -2885,13 +3075,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="89294733"/>
@@ -2935,13 +3126,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="64581281"/>
@@ -2969,37 +3161,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3008,7 +3209,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3016,7 +3217,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3037,6 +3238,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -3046,7 +3248,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Resumen Exp2'!C16</c:f>
+              <c:f>'Resumen Exp2'!$C$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3057,7 +3259,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -3065,15 +3267,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3081,8 +3291,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3091,7 +3302,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Resumen Exp2'!$B$17:$B$18</c:f>
+              <c:f>'Resumen Exp2'!$B$16:$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -3105,7 +3316,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Resumen Exp2'!$C$17:$C$18</c:f>
+              <c:f>'Resumen Exp2'!$C$16:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3118,13 +3329,18 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-36CE-47C6-8F72-A7236B85B402}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Resumen Exp2'!D16</c:f>
+              <c:f>'Resumen Exp2'!$D$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3135,7 +3351,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c0504d"/>
+              <a:srgbClr val="C0504D"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -3143,15 +3359,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3159,8 +3383,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3169,7 +3394,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Resumen Exp2'!$B$17:$B$18</c:f>
+              <c:f>'Resumen Exp2'!$B$16:$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -3183,7 +3408,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Resumen Exp2'!$D$17:$D$18</c:f>
+              <c:f>'Resumen Exp2'!$D$16:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -3196,9 +3421,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-36CE-47C6-8F72-A7236B85B402}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="66117048"/>
         <c:axId val="11485639"/>
       </c:barChart>
@@ -3226,13 +3463,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="11485639"/>
@@ -3276,13 +3514,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="66117048"/>
@@ -3310,37 +3549,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3349,7 +3597,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3357,7 +3605,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3378,6 +3626,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -3386,7 +3635,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase1 Exp2'!C5</c:f>
+              <c:f>'Fase1 Exp2'!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3396,12 +3645,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3410,15 +3656,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3426,8 +3680,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3435,9 +3690,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase1 Exp2'!$B$6:$B$12</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
@@ -3460,8 +3716,8 @@
                 <c:pt idx="6">
                   <c:v>9</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3494,13 +3750,18 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6DFA-46DC-AEDC-8DCE0BB66288}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase1 Exp2'!D5</c:f>
+              <c:f>'Fase1 Exp2'!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3510,12 +3771,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="be4b48"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="BE4B48"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3524,15 +3782,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3540,8 +3806,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3549,9 +3816,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase1 Exp2'!$B$6:$B$12</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
@@ -3574,8 +3842,8 @@
                 <c:pt idx="6">
                   <c:v>9</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3608,7 +3876,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6DFA-46DC-AEDC-8DCE0BB66288}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -3616,7 +3897,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="47161259"/>
         <c:axId val="45043499"/>
       </c:lineChart>
@@ -3644,13 +3925,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="45043499"/>
@@ -3694,13 +3976,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="47161259"/>
@@ -3728,37 +4011,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -3767,7 +4059,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3775,7 +4067,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -3796,6 +4088,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -3804,7 +4097,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase1 Exp2'!D15</c:f>
+              <c:f>'Fase1 Exp2'!$D$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3814,12 +4107,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -3828,15 +4118,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -3844,8 +4142,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -3853,9 +4152,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase1 Exp2'!$B$16:$B$25</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -3887,8 +4187,8 @@
                 <c:pt idx="9">
                   <c:v>10</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3930,7 +4230,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5A90-430C-933D-B729F9B50F59}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -3938,7 +4251,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="86252258"/>
         <c:axId val="51897546"/>
       </c:lineChart>
@@ -3966,13 +4279,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="51897546"/>
@@ -4016,13 +4330,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="86252258"/>
@@ -4050,37 +4365,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -4089,7 +4413,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -4097,7 +4421,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -4118,6 +4442,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -4126,7 +4451,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase2 Exp2'!C5</c:f>
+              <c:f>'Fase2 Exp2'!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4136,12 +4461,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="4A7EBB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4150,15 +4472,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -4166,8 +4496,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -4175,9 +4506,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase2 Exp2'!$B$6:$B$28</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
@@ -4248,8 +4580,8 @@
                 <c:pt idx="22">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -4330,13 +4662,18 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-24ED-47D9-A5DC-2E066257DE9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Fase2 Exp2'!D5</c:f>
+              <c:f>'Fase2 Exp2'!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4346,12 +4683,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="be4b48"/>
-            </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="be4b48"/>
+                <a:srgbClr val="BE4B48"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -4360,15 +4694,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -4376,8 +4718,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -4385,9 +4728,10 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>'Fase2 Exp2'!$B$6:$B$28</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
@@ -4458,8 +4802,8 @@
                 <c:pt idx="22">
                   <c:v>32</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -4540,7 +4884,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-24ED-47D9-A5DC-2E066257DE9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -4548,7 +4905,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="6162401"/>
         <c:axId val="78647709"/>
       </c:lineChart>
@@ -4576,13 +4933,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="78647709"/>
@@ -4626,13 +4984,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="6162401"/>
@@ -4660,35 +5019,42 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -4702,14 +5068,20 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8435520" y="762120"/>
-        <a:ext cx="5759640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4723,7 +5095,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -4737,14 +5109,20 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="762120"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4767,14 +5145,20 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>167400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="2666880"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4788,7 +5172,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -4802,14 +5186,20 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 1"/>
+        <xdr:cNvPr id="3" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="762120"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4832,14 +5222,20 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>167400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 2"/>
+        <xdr:cNvPr id="4" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="5905440"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4853,7 +5249,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
@@ -4867,14 +5263,20 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 1"/>
+        <xdr:cNvPr id="5" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8435520" y="762120"/>
-        <a:ext cx="5759640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4888,7 +5290,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -4902,14 +5304,20 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 1"/>
+        <xdr:cNvPr id="6" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="762120"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4932,14 +5340,20 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>167400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 2"/>
+        <xdr:cNvPr id="7" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="2666880"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4953,7 +5367,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -4967,14 +5381,20 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 1"/>
+        <xdr:cNvPr id="8" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="762120"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4997,14 +5417,20 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>167400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 2"/>
+        <xdr:cNvPr id="9" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6673320" y="5715000"/>
-        <a:ext cx="6119640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5018,41 +5444,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -5060,12 +5486,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -5094,7 +5520,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -5115,7 +5541,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -5166,7 +5592,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -5184,40 +5610,39 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:G18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:7" ht="19" x14ac:dyDescent="0.4">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -5227,181 +5652,166 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7">
         <v>1421</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7">
         <v>8291</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="7">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D7" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>200</v>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(D7&lt;=E7,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="9">
+        <v>20.36</v>
+      </c>
+      <c r="D8" s="9">
+        <v>14.82</v>
+      </c>
+      <c r="E8" s="9">
+        <v>350</v>
+      </c>
+      <c r="F8" t="str">
+        <f>IF(D8&lt;=E8,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7">
+        <v>29898</v>
+      </c>
+      <c r="D9" s="7">
+        <v>255708</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="9">
+        <v>49.8</v>
+      </c>
+      <c r="D10" s="9">
+        <v>142.1</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1421</v>
+      </c>
+      <c r="D16" s="7">
         <v>801</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>4637</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F7" s="0" t="str">
-        <f aca="false">IF(D7&gt;=E7,"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="F8" s="0" t="str">
-        <f aca="false">IF(D8&lt;=E8,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>20.36</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>350</v>
-      </c>
-      <c r="F9" s="0" t="str">
-        <f aca="false">IF(D9&lt;=E9,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>29898</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>255708</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>1421</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="6" t="n">
+      <c r="C17" s="7">
         <v>8291</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D17" s="7">
         <v>4637</v>
       </c>
     </row>
@@ -5409,58 +5819,50 @@
   <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B13:G13"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:F12">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="F6:F11">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"CUMPLE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"NO CUMPLE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:I24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:9" ht="19" x14ac:dyDescent="0.4">
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -5470,258 +5872,258 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>82</v>
+      </c>
+      <c r="D6" s="7">
+        <v>31</v>
+      </c>
+      <c r="E6" s="7">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="n">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="9">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1288</v>
+      </c>
+      <c r="D7" s="9">
+        <v>714</v>
+      </c>
+      <c r="E7" s="9">
+        <v>3.9E-2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="7">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1326</v>
+      </c>
+      <c r="D8" s="7">
+        <v>782</v>
+      </c>
+      <c r="E8" s="7">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="9">
+        <v>7</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1322</v>
+      </c>
+      <c r="D9" s="9">
+        <v>702</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="7">
+        <v>8</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1322</v>
+      </c>
+      <c r="D10" s="7">
+        <v>737</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="9">
+        <v>9</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1325</v>
+      </c>
+      <c r="D11" s="9">
+        <v>757</v>
+      </c>
+      <c r="E11" s="9">
+        <v>4.7E-2</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1945</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1115</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="7">
+        <v>2</v>
+      </c>
+      <c r="C16" s="7">
+        <v>280</v>
+      </c>
+      <c r="D16" s="7">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="9">
+        <v>3</v>
+      </c>
+      <c r="C17" s="9">
+        <v>1492</v>
+      </c>
+      <c r="D17" s="9">
+        <v>26.48</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="7">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="n">
+      <c r="C18" s="7">
+        <v>1562</v>
+      </c>
+      <c r="D18" s="7">
+        <v>32.479999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="9">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>1288</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>714</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="n">
+      <c r="C19" s="9">
+        <v>1422</v>
+      </c>
+      <c r="D19" s="9">
+        <v>31.26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="7">
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>1326</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>782</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="n">
+      <c r="C20" s="7">
+        <v>1460</v>
+      </c>
+      <c r="D20" s="7">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="9">
         <v>7</v>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>1322</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>702</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="n">
+      <c r="C21" s="9">
+        <v>1514</v>
+      </c>
+      <c r="D21" s="9">
+        <v>27.79</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="7">
         <v>8</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>1322</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>737</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="n">
+      <c r="C22" s="7">
+        <v>3660</v>
+      </c>
+      <c r="D22" s="7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="9">
         <v>9</v>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>1325</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>757</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="n">
+      <c r="C23" s="9">
+        <v>9250</v>
+      </c>
+      <c r="D23" s="9">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" s="7">
         <v>10</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>1945</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>1115</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>35.1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>1492</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>26.48</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>1562</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>32.48</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>1422</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>31.26</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>1460</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>25.25</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>1514</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>27.79</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>3660</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>9250</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>16.39</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="7">
         <v>9258</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7">
         <v>15.19</v>
       </c>
     </row>
@@ -5731,48 +6133,40 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B14:F14"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:I63"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:9" ht="19" x14ac:dyDescent="0.4">
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -5782,864 +6176,864 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7">
+        <v>8293</v>
+      </c>
+      <c r="D6" s="7">
+        <v>4635</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="9">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9">
+        <v>8305</v>
+      </c>
+      <c r="D7" s="9">
+        <v>4629</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="7">
+        <v>13</v>
+      </c>
+      <c r="C8" s="7">
+        <v>8296</v>
+      </c>
+      <c r="D8" s="7">
+        <v>4553</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.1E-2</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="9">
+        <v>14</v>
+      </c>
+      <c r="C9" s="9">
+        <v>8270</v>
+      </c>
+      <c r="D9" s="9">
+        <v>4768</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="7">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>8278</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4556</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="9">
+        <v>16</v>
+      </c>
+      <c r="C11" s="9">
+        <v>8289</v>
+      </c>
+      <c r="D11" s="9">
+        <v>4629</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B12" s="7">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7">
+        <v>8291</v>
+      </c>
+      <c r="D12" s="7">
+        <v>4608</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="9">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9">
+        <v>8279</v>
+      </c>
+      <c r="D13" s="9">
+        <v>4666</v>
+      </c>
+      <c r="E13" s="9">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="7">
+        <v>19</v>
+      </c>
+      <c r="C14" s="7">
+        <v>8288</v>
+      </c>
+      <c r="D14" s="7">
+        <v>4660</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="9">
+        <v>20</v>
+      </c>
+      <c r="C15" s="9">
+        <v>8298</v>
+      </c>
+      <c r="D15" s="9">
+        <v>4556</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="7">
+        <v>21</v>
+      </c>
+      <c r="C16" s="7">
+        <v>8283</v>
+      </c>
+      <c r="D16" s="7">
+        <v>4743</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="9">
+        <v>22</v>
+      </c>
+      <c r="C17" s="9">
+        <v>8275</v>
+      </c>
+      <c r="D17" s="9">
+        <v>4647</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="7">
+        <v>23</v>
+      </c>
+      <c r="C18" s="7">
+        <v>8317</v>
+      </c>
+      <c r="D18" s="7">
+        <v>4534</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.1E-2</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="9">
+        <v>24</v>
+      </c>
+      <c r="C19" s="9">
+        <v>8297</v>
+      </c>
+      <c r="D19" s="9">
+        <v>4695</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="7">
+        <v>25</v>
+      </c>
+      <c r="C20" s="7">
+        <v>8273</v>
+      </c>
+      <c r="D20" s="7">
+        <v>4708</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="9">
+        <v>26</v>
+      </c>
+      <c r="C21" s="9">
+        <v>8303</v>
+      </c>
+      <c r="D21" s="9">
+        <v>4766</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="7">
+        <v>27</v>
+      </c>
+      <c r="C22" s="7">
+        <v>8285</v>
+      </c>
+      <c r="D22" s="7">
+        <v>4542</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="9">
+        <v>28</v>
+      </c>
+      <c r="C23" s="9">
+        <v>8299</v>
+      </c>
+      <c r="D23" s="9">
+        <v>4662</v>
+      </c>
+      <c r="E23" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="7">
+        <v>29</v>
+      </c>
+      <c r="C24" s="7">
+        <v>8293</v>
+      </c>
+      <c r="D24" s="7">
+        <v>4677</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="9">
+        <v>30</v>
+      </c>
+      <c r="C25" s="9">
+        <v>8306</v>
+      </c>
+      <c r="D25" s="9">
+        <v>4652</v>
+      </c>
+      <c r="E25" s="9">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="7">
+        <v>31</v>
+      </c>
+      <c r="C26" s="7">
+        <v>8290</v>
+      </c>
+      <c r="D26" s="7">
+        <v>4544</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="9">
         <v>32</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="C27" s="9">
+        <v>8291</v>
+      </c>
+      <c r="D27" s="9">
+        <v>4616</v>
+      </c>
+      <c r="E27" s="9">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="n">
+      <c r="G27" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="7">
+        <v>33</v>
+      </c>
+      <c r="C28" s="7">
+        <v>8302</v>
+      </c>
+      <c r="D28" s="7">
+        <v>4606</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="9">
+        <v>34</v>
+      </c>
+      <c r="C29" s="9">
+        <v>3934</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2286</v>
+      </c>
+      <c r="E29" s="9">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="7">
         <v>11</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>8293</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>4635</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="C33" s="7">
+        <v>9242</v>
+      </c>
+      <c r="D33" s="7">
+        <v>15.85</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="9">
+        <v>12</v>
+      </c>
+      <c r="C34" s="9">
+        <v>9408</v>
+      </c>
+      <c r="D34" s="9">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="7">
+        <v>13</v>
+      </c>
+      <c r="C35" s="7">
+        <v>9182</v>
+      </c>
+      <c r="D35" s="7">
+        <v>16.809999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="9">
+        <v>14</v>
+      </c>
+      <c r="C36" s="9">
+        <v>9216</v>
+      </c>
+      <c r="D36" s="9">
+        <v>15.86</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="7">
+        <v>15</v>
+      </c>
+      <c r="C37" s="7">
+        <v>9260</v>
+      </c>
+      <c r="D37" s="7">
+        <v>14.92</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="9">
+        <v>16</v>
+      </c>
+      <c r="C38" s="9">
+        <v>9322</v>
+      </c>
+      <c r="D38" s="9">
+        <v>15.72</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="7">
+        <v>17</v>
+      </c>
+      <c r="C39" s="7">
+        <v>9334</v>
+      </c>
+      <c r="D39" s="7">
+        <v>14.42</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="9">
+        <v>18</v>
+      </c>
+      <c r="C40" s="9">
+        <v>9198</v>
+      </c>
+      <c r="D40" s="9">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="7">
+        <v>19</v>
+      </c>
+      <c r="C41" s="7">
+        <v>9334</v>
+      </c>
+      <c r="D41" s="7">
+        <v>15.37</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="9">
+        <v>20</v>
+      </c>
+      <c r="C42" s="9">
+        <v>9208</v>
+      </c>
+      <c r="D42" s="9">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="7">
+        <v>21</v>
+      </c>
+      <c r="C43" s="7">
+        <v>9172</v>
+      </c>
+      <c r="D43" s="7">
+        <v>14.36</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="9">
+        <v>22</v>
+      </c>
+      <c r="C44" s="9">
+        <v>9450</v>
+      </c>
+      <c r="D44" s="9">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="7">
+        <v>23</v>
+      </c>
+      <c r="C45" s="7">
+        <v>9506</v>
+      </c>
+      <c r="D45" s="7">
+        <v>15.81</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="9">
+        <v>24</v>
+      </c>
+      <c r="C46" s="9">
+        <v>9376</v>
+      </c>
+      <c r="D46" s="9">
+        <v>14.77</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="7">
+        <v>25</v>
+      </c>
+      <c r="C47" s="7">
+        <v>9086</v>
+      </c>
+      <c r="D47" s="7">
+        <v>13.95</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="9">
+        <v>26</v>
+      </c>
+      <c r="C48" s="9">
+        <v>9416</v>
+      </c>
+      <c r="D48" s="9">
+        <v>13.12</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B49" s="7">
+        <v>27</v>
+      </c>
+      <c r="C49" s="7">
+        <v>9260</v>
+      </c>
+      <c r="D49" s="7">
+        <v>13.08</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B50" s="9">
+        <v>28</v>
+      </c>
+      <c r="C50" s="9">
+        <v>9264</v>
+      </c>
+      <c r="D50" s="9">
+        <v>12.51</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B51" s="7">
+        <v>29</v>
+      </c>
+      <c r="C51" s="7">
+        <v>9206</v>
+      </c>
+      <c r="D51" s="7">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B52" s="9">
+        <v>30</v>
+      </c>
+      <c r="C52" s="9">
+        <v>9036</v>
+      </c>
+      <c r="D52" s="9">
+        <v>11.56</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B53" s="7">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7">
+        <v>9490</v>
+      </c>
+      <c r="D53" s="7">
+        <v>14.22</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="9">
+        <v>32</v>
+      </c>
+      <c r="C54" s="9">
+        <v>3912</v>
+      </c>
+      <c r="D54" s="9">
+        <v>22.76</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B55" s="7">
+        <v>33</v>
+      </c>
+      <c r="C55" s="7">
+        <v>9460</v>
+      </c>
+      <c r="D55" s="7">
+        <v>15.63</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B56" s="9">
+        <v>34</v>
+      </c>
+      <c r="C56" s="9">
+        <v>6262</v>
+      </c>
+      <c r="D56" s="9">
+        <v>13.49</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B57" s="7">
+        <v>35</v>
+      </c>
+      <c r="C57" s="7">
+        <v>8184</v>
+      </c>
+      <c r="D57" s="7">
+        <v>17.53</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B58" s="9">
+        <v>36</v>
+      </c>
+      <c r="C58" s="9">
+        <v>8734</v>
+      </c>
+      <c r="D58" s="9">
+        <v>14.34</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B59" s="7">
+        <v>37</v>
+      </c>
+      <c r="C59" s="7">
+        <v>4352</v>
+      </c>
+      <c r="D59" s="7">
+        <v>25.91</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B60" s="9">
+        <v>38</v>
+      </c>
+      <c r="C60" s="9">
+        <v>9234</v>
+      </c>
+      <c r="D60" s="9">
+        <v>14.71</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B61" s="7">
+        <v>39</v>
+      </c>
+      <c r="C61" s="7">
+        <v>2946</v>
+      </c>
+      <c r="D61" s="7">
+        <v>13.32</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B62" s="9">
+        <v>40</v>
+      </c>
+      <c r="C62" s="9">
+        <v>7614</v>
+      </c>
+      <c r="D62" s="9">
+        <v>18.11</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B63" s="7">
         <v>41</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>8305</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>4629</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>8296</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>4553</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>8270</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>4768</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>8278</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>4556</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>8289</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>4629</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>8291</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>4608</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>8279</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>4666</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>8288</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>4660</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>8298</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>4556</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>8283</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>4743</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>8275</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>4647</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>8317</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>4534</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>8297</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>4695</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>8273</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>4708</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>8303</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>4766</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>8285</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>4542</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>8299</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>4662</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>8293</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>4677</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>8306</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>4652</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>8290</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>4544</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>8291</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>4616</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>8302</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>4606</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>3934</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>2286</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>9242</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>15.85</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>9408</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>9182</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>16.81</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>9216</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>15.86</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>9260</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>14.92</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>9322</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>15.72</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>9334</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>14.42</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>9198</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>9334</v>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>15.37</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>9208</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>9172</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>14.36</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C44" s="8" t="n">
-        <v>9450</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>13.26</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>9506</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>15.81</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C46" s="8" t="n">
-        <v>9376</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>14.77</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>9086</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>13.95</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>9416</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>13.12</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>9260</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>13.08</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>9264</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>12.51</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>9206</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>11.51</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>9036</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>11.56</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>9490</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>14.22</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>3912</v>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>22.76</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>9460</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>15.63</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>6262</v>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>13.49</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="C57" s="6" t="n">
-        <v>8184</v>
-      </c>
-      <c r="D57" s="6" t="n">
-        <v>17.53</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>8734</v>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>14.34</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="C59" s="6" t="n">
-        <v>4352</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>25.91</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="C60" s="8" t="n">
-        <v>9234</v>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>14.71</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>2946</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>13.32</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="C62" s="8" t="n">
-        <v>7614</v>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>18.11</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="C63" s="6" t="n">
+      <c r="C63" s="7">
         <v>44</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="7">
         <v>24</v>
       </c>
     </row>
@@ -6649,43 +7043,35 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B31:F31"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:G18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B2:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:7" ht="19" x14ac:dyDescent="0.4">
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -6695,181 +7081,163 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7">
         <v>1328</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7">
         <v>8230</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2.3E-2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>200</v>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(D7&lt;=E7,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="9">
+        <v>6.72</v>
+      </c>
+      <c r="D8" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="E8" s="9">
+        <v>350</v>
+      </c>
+      <c r="F8" t="str">
+        <f>IF(D8&lt;=E8,"CUMPLE","NO CUMPLE")</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7">
+        <v>39272</v>
+      </c>
+      <c r="D9" s="7">
+        <v>169232</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="9">
+        <v>65.5</v>
+      </c>
+      <c r="D10" s="9">
+        <v>94</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B14" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1328</v>
+      </c>
+      <c r="D16" s="7">
         <v>736</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>4604</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F7" s="0" t="str">
-        <f aca="false">IF(D7&gt;=E7,"CUMPLE","NO CUMPLE")</f>
-        <v>NO CUMPLE</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="F8" s="0" t="str">
-        <f aca="false">IF(D8&lt;=E8,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>350</v>
-      </c>
-      <c r="F9" s="0" t="str">
-        <f aca="false">IF(D9&lt;=E9,"CUMPLE","NO CUMPLE")</f>
-        <v>CUMPLE</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>39272</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>169232</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>1328</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="6" t="n">
+      <c r="C17" s="7">
         <v>8230</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D17" s="7">
         <v>4604</v>
       </c>
     </row>
@@ -6877,58 +7245,50 @@
   <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B13:G13"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:F12">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="F6:F11">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"CUMPLE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"NO CUMPLE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:I25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:9" ht="19" x14ac:dyDescent="0.4">
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -6938,269 +7298,269 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7">
+        <v>242</v>
+      </c>
+      <c r="D6" s="7">
+        <v>112</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="n">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="9">
+        <v>4</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1326</v>
+      </c>
+      <c r="D7" s="9">
+        <v>728</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="7">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1333</v>
+      </c>
+      <c r="D8" s="7">
+        <v>757</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1325</v>
+      </c>
+      <c r="D9" s="9">
+        <v>748</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="7">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1332</v>
+      </c>
+      <c r="D10" s="7">
+        <v>732</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="9">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1327</v>
+      </c>
+      <c r="D11" s="9">
+        <v>726</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B12" s="7">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1324</v>
+      </c>
+      <c r="D12" s="7">
+        <v>728</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="7">
+        <v>1</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1084</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="9">
+        <v>2</v>
+      </c>
+      <c r="C17" s="9">
+        <v>1476</v>
+      </c>
+      <c r="D17" s="9">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>242</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>112</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="n">
+      <c r="C18" s="7">
+        <v>1614</v>
+      </c>
+      <c r="D18" s="7">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="9">
         <v>4</v>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>1326</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>728</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="n">
+      <c r="C19" s="9">
+        <v>1360</v>
+      </c>
+      <c r="D19" s="9">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>1333</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>757</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="n">
+      <c r="C20" s="7">
+        <v>1504</v>
+      </c>
+      <c r="D20" s="7">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="9">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>1325</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>748</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="n">
+      <c r="C21" s="9">
+        <v>1422</v>
+      </c>
+      <c r="D21" s="9">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>1332</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>732</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="n">
+      <c r="C22" s="7">
+        <v>2780</v>
+      </c>
+      <c r="D22" s="7">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="9">
         <v>8</v>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>1327</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>726</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="n">
+      <c r="C23" s="9">
+        <v>9456</v>
+      </c>
+      <c r="D23" s="9">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>1324</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>728</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>1084</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>1476</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>5.48</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>1614</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>5.52</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>1360</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>5.19</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>1504</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>5.97</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>1422</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>6.44</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>2780</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>9456</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="7">
         <v>9294</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7">
         <v>7.29</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="n">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="9">
         <v>10</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9">
         <v>9282</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="9">
         <v>6.87</v>
       </c>
     </row>
@@ -7210,48 +7570,40 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B14:F14"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:I51"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:9" ht="19" x14ac:dyDescent="0.4">
+      <c r="B2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -7261,723 +7613,723 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7">
+        <v>5130</v>
+      </c>
+      <c r="D6" s="7">
+        <v>2943</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="9">
+        <v>11</v>
+      </c>
+      <c r="C7" s="9">
+        <v>8321</v>
+      </c>
+      <c r="D7" s="9">
+        <v>4643</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="7">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7">
+        <v>8300</v>
+      </c>
+      <c r="D8" s="7">
+        <v>4703</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="9">
+        <v>13</v>
+      </c>
+      <c r="C9" s="9">
+        <v>8321</v>
+      </c>
+      <c r="D9" s="9">
+        <v>4668</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="7">
+        <v>14</v>
+      </c>
+      <c r="C10" s="7">
+        <v>8304</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4548</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="9">
+        <v>15</v>
+      </c>
+      <c r="C11" s="9">
+        <v>8316</v>
+      </c>
+      <c r="D11" s="9">
+        <v>4721</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B12" s="7">
+        <v>16</v>
+      </c>
+      <c r="C12" s="7">
+        <v>8303</v>
+      </c>
+      <c r="D12" s="7">
+        <v>4759</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="9">
+        <v>17</v>
+      </c>
+      <c r="C13" s="9">
+        <v>8310</v>
+      </c>
+      <c r="D13" s="9">
+        <v>4684</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="7">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7">
+        <v>8309</v>
+      </c>
+      <c r="D14" s="7">
+        <v>4612</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="9">
+        <v>19</v>
+      </c>
+      <c r="C15" s="9">
+        <v>8330</v>
+      </c>
+      <c r="D15" s="9">
+        <v>4682</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="7">
+        <v>20</v>
+      </c>
+      <c r="C16" s="7">
+        <v>8293</v>
+      </c>
+      <c r="D16" s="7">
+        <v>4777</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="9">
+        <v>21</v>
+      </c>
+      <c r="C17" s="9">
+        <v>8311</v>
+      </c>
+      <c r="D17" s="9">
+        <v>4573</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="7">
+        <v>22</v>
+      </c>
+      <c r="C18" s="7">
+        <v>8313</v>
+      </c>
+      <c r="D18" s="7">
+        <v>4594</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="9">
+        <v>23</v>
+      </c>
+      <c r="C19" s="9">
+        <v>8308</v>
+      </c>
+      <c r="D19" s="9">
+        <v>4680</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="7">
+        <v>24</v>
+      </c>
+      <c r="C20" s="7">
+        <v>8312</v>
+      </c>
+      <c r="D20" s="7">
+        <v>4548</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="9">
+        <v>25</v>
+      </c>
+      <c r="C21" s="9">
+        <v>8306</v>
+      </c>
+      <c r="D21" s="9">
+        <v>4670</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="7">
+        <v>26</v>
+      </c>
+      <c r="C22" s="7">
+        <v>8308</v>
+      </c>
+      <c r="D22" s="7">
+        <v>4633</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="9">
+        <v>27</v>
+      </c>
+      <c r="C23" s="9">
+        <v>8312</v>
+      </c>
+      <c r="D23" s="9">
+        <v>4596</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="7">
+        <v>28</v>
+      </c>
+      <c r="C24" s="7">
+        <v>8310</v>
+      </c>
+      <c r="D24" s="7">
+        <v>4589</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="9">
+        <v>29</v>
+      </c>
+      <c r="C25" s="9">
+        <v>8313</v>
+      </c>
+      <c r="D25" s="9">
+        <v>4729</v>
+      </c>
+      <c r="E25" s="9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="7">
+        <v>30</v>
+      </c>
+      <c r="C26" s="7">
+        <v>8311</v>
+      </c>
+      <c r="D26" s="7">
+        <v>4623</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="9">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9">
+        <v>6695</v>
+      </c>
+      <c r="D27" s="9">
+        <v>3729</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="7">
         <v>32</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>5130</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>2943</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="C28" s="7">
+        <v>8152</v>
+      </c>
+      <c r="D28" s="7">
+        <v>4524</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.3E-2</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="7">
         <v>5000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="n">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="7">
         <v>11</v>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>8321</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>4643</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="n">
+      <c r="C32" s="7">
+        <v>9328</v>
+      </c>
+      <c r="D32" s="7">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="9">
         <v>12</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>8300</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>4703</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="n">
+      <c r="C33" s="9">
+        <v>9208</v>
+      </c>
+      <c r="D33" s="9">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="7">
         <v>13</v>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>8321</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>4668</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="n">
+      <c r="C34" s="7">
+        <v>9480</v>
+      </c>
+      <c r="D34" s="7">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="9">
         <v>14</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>8304</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>4548</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="n">
+      <c r="C35" s="9">
+        <v>9552</v>
+      </c>
+      <c r="D35" s="9">
+        <v>6.91</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="7">
         <v>15</v>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>8316</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>4721</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="n">
+      <c r="C36" s="7">
+        <v>9140</v>
+      </c>
+      <c r="D36" s="7">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="9">
         <v>16</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>8303</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>4759</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="n">
+      <c r="C37" s="9">
+        <v>9406</v>
+      </c>
+      <c r="D37" s="9">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="7">
         <v>17</v>
       </c>
-      <c r="C13" s="8" t="n">
-        <v>8310</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>4684</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="n">
+      <c r="C38" s="7">
+        <v>9582</v>
+      </c>
+      <c r="D38" s="7">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="9">
         <v>18</v>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>8309</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>4612</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="n">
+      <c r="C39" s="9">
+        <v>9148</v>
+      </c>
+      <c r="D39" s="9">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="7">
         <v>19</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <v>8330</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>4682</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="n">
+      <c r="C40" s="7">
+        <v>9162</v>
+      </c>
+      <c r="D40" s="7">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="9">
         <v>20</v>
       </c>
-      <c r="C16" s="6" t="n">
-        <v>8293</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>4777</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="n">
+      <c r="C41" s="9">
+        <v>9288</v>
+      </c>
+      <c r="D41" s="9">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="7">
         <v>21</v>
       </c>
-      <c r="C17" s="8" t="n">
-        <v>8311</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>4573</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="n">
+      <c r="C42" s="7">
+        <v>9270</v>
+      </c>
+      <c r="D42" s="7">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="9">
         <v>22</v>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>8313</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>4594</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="n">
+      <c r="C43" s="9">
+        <v>9320</v>
+      </c>
+      <c r="D43" s="9">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="7">
         <v>23</v>
       </c>
-      <c r="C19" s="8" t="n">
-        <v>8308</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>4680</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="n">
+      <c r="C44" s="7">
+        <v>9194</v>
+      </c>
+      <c r="D44" s="7">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="9">
         <v>24</v>
       </c>
-      <c r="C20" s="6" t="n">
-        <v>8312</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>4548</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="n">
+      <c r="C45" s="9">
+        <v>9078</v>
+      </c>
+      <c r="D45" s="9">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="7">
         <v>25</v>
       </c>
-      <c r="C21" s="8" t="n">
-        <v>8306</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>4670</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="n">
+      <c r="C46" s="7">
+        <v>9358</v>
+      </c>
+      <c r="D46" s="7">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="9">
         <v>26</v>
       </c>
-      <c r="C22" s="6" t="n">
-        <v>8308</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>4633</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="n">
+      <c r="C47" s="9">
+        <v>9350</v>
+      </c>
+      <c r="D47" s="9">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="7">
         <v>27</v>
       </c>
-      <c r="C23" s="8" t="n">
-        <v>8312</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>4596</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="n">
+      <c r="C48" s="7">
+        <v>9402</v>
+      </c>
+      <c r="D48" s="7">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B49" s="9">
         <v>28</v>
       </c>
-      <c r="C24" s="6" t="n">
-        <v>8310</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>4589</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="n">
+      <c r="C49" s="9">
+        <v>9200</v>
+      </c>
+      <c r="D49" s="9">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B50" s="7">
         <v>29</v>
       </c>
-      <c r="C25" s="8" t="n">
-        <v>8313</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>4729</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>8311</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>4623</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>6695</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>3729</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>8152</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>4524</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F28" s="6" t="s">
+      <c r="C50" s="7">
+        <v>1732</v>
+      </c>
+      <c r="D50" s="7">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B51" s="9">
         <v>46</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>9328</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>9208</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>9480</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>6.84</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>9552</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>6.91</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>9140</v>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>9406</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>9582</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>6.86</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>9148</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>6.71</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>9162</v>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>9288</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>9270</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C43" s="8" t="n">
-        <v>9320</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>6.41</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>9194</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C45" s="8" t="n">
-        <v>9078</v>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>6.76</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>9358</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C47" s="8" t="n">
-        <v>9350</v>
-      </c>
-      <c r="D47" s="8" t="n">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C48" s="6" t="n">
-        <v>9402</v>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>6.36</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C49" s="8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="D49" s="8" t="n">
-        <v>6.27</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="C50" s="6" t="n">
-        <v>1732</v>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>6.47</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="C51" s="8" t="n">
+      <c r="C51" s="9">
         <v>34</v>
       </c>
-      <c r="D51" s="8" t="n">
+      <c r="D51" s="9">
         <v>249.65</v>
       </c>
     </row>
@@ -7987,13 +8339,8 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B30:F30"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>